--- a/data/raw/September_26_Utilities_Tracking.xlsx
+++ b/data/raw/September_26_Utilities_Tracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UTILITIES\Tracking\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57523C63-E3C6-4023-AACF-240A803BFE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98FAFC3-922E-4B07-B551-F24B26FE50EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="579" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
           </rPr>
           <t xml:space="preserve">Tank A 0 kgs 
 Tank B 0 kgs
-Tank C 17900 Kgs
+Tank C 16300 Kgs
 mobile approx 0 Kgs
 19600  kgs after adjustment for MT mobile weight
 </t>
@@ -861,7 +861,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="329">
   <si>
     <t>UTILITY ANALYSIS</t>
   </si>
@@ -9175,15 +9175,60 @@
     <xf numFmtId="3" fontId="15" fillId="31" borderId="130" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="146" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9205,9 +9250,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9223,45 +9265,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="124" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="77" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="78" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="79" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="100" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9379,15 +9382,39 @@
     <xf numFmtId="0" fontId="70" fillId="12" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9397,30 +9424,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9475,6 +9478,30 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="122" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9535,35 +9562,8 @@
     <xf numFmtId="0" fontId="95" fillId="16" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="72" fillId="18" borderId="123" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="32" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="146" fillId="31" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -9574,7 +9574,7 @@
     <cellStyle name="Normal_February04" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
-  <dxfs count="119">
+  <dxfs count="117">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10053,26 +10053,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12923,53 +12903,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.2">
-      <c r="B1" s="897" t="s">
+      <c r="B1" s="912" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="897"/>
-      <c r="D1" s="897"/>
-      <c r="E1" s="897"/>
-      <c r="F1" s="897"/>
-      <c r="G1" s="897"/>
-      <c r="H1" s="897"/>
-      <c r="I1" s="897"/>
-      <c r="J1" s="897"/>
-      <c r="K1" s="897"/>
-      <c r="L1" s="897"/>
-      <c r="M1" s="897"/>
+      <c r="C1" s="912"/>
+      <c r="D1" s="912"/>
+      <c r="E1" s="912"/>
+      <c r="F1" s="912"/>
+      <c r="G1" s="912"/>
+      <c r="H1" s="912"/>
+      <c r="I1" s="912"/>
+      <c r="J1" s="912"/>
+      <c r="K1" s="912"/>
+      <c r="L1" s="912"/>
+      <c r="M1" s="912"/>
       <c r="N1" s="363"/>
-      <c r="O1" s="898" t="str">
+      <c r="O1" s="913" t="str">
         <f>B1</f>
         <v>ENTRIES FOR DAILY CONS. MONITOR</v>
       </c>
-      <c r="P1" s="898"/>
-      <c r="Q1" s="898"/>
-      <c r="R1" s="898"/>
-      <c r="S1" s="898"/>
-      <c r="T1" s="898"/>
-      <c r="U1" s="898"/>
-      <c r="V1" s="898"/>
-      <c r="W1" s="898"/>
-      <c r="X1" s="898"/>
-      <c r="Y1" s="898"/>
-      <c r="Z1" s="898"/>
-      <c r="AA1" s="898"/>
-      <c r="AB1" s="898"/>
+      <c r="P1" s="913"/>
+      <c r="Q1" s="913"/>
+      <c r="R1" s="913"/>
+      <c r="S1" s="913"/>
+      <c r="T1" s="913"/>
+      <c r="U1" s="913"/>
+      <c r="V1" s="913"/>
+      <c r="W1" s="913"/>
+      <c r="X1" s="913"/>
+      <c r="Y1" s="913"/>
+      <c r="Z1" s="913"/>
+      <c r="AA1" s="913"/>
+      <c r="AB1" s="913"/>
     </row>
     <row r="2" spans="1:44" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="815"/>
       <c r="F2" s="364"/>
       <c r="G2" s="365"/>
-      <c r="O2" s="906" t="s">
+      <c r="O2" s="920" t="s">
         <v>231</v>
       </c>
-      <c r="P2" s="906"/>
-      <c r="Q2" s="906"/>
-      <c r="R2" s="906"/>
-      <c r="S2" s="906"/>
-      <c r="T2" s="906"/>
-      <c r="U2" s="906"/>
-      <c r="V2" s="906"/>
+      <c r="P2" s="920"/>
+      <c r="Q2" s="920"/>
+      <c r="R2" s="920"/>
+      <c r="S2" s="920"/>
+      <c r="T2" s="920"/>
+      <c r="U2" s="920"/>
+      <c r="V2" s="920"/>
     </row>
     <row r="3" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="366"/>
@@ -12987,50 +12967,50 @@
         <v>22</v>
       </c>
       <c r="K3" s="369"/>
-      <c r="L3" s="911" t="s">
+      <c r="L3" s="903" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="912"/>
-      <c r="N3" s="913"/>
-      <c r="O3" s="899" t="s">
+      <c r="M3" s="904"/>
+      <c r="N3" s="905"/>
+      <c r="O3" s="914" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="899"/>
-      <c r="Q3" s="899"/>
-      <c r="R3" s="899"/>
-      <c r="S3" s="899"/>
-      <c r="T3" s="899"/>
-      <c r="U3" s="899"/>
-      <c r="V3" s="899"/>
-      <c r="W3" s="899"/>
-      <c r="X3" s="899"/>
-      <c r="Y3" s="899"/>
-      <c r="Z3" s="899"/>
-      <c r="AA3" s="899"/>
-      <c r="AB3" s="899"/>
-      <c r="AC3" s="899"/>
+      <c r="P3" s="914"/>
+      <c r="Q3" s="914"/>
+      <c r="R3" s="914"/>
+      <c r="S3" s="914"/>
+      <c r="T3" s="914"/>
+      <c r="U3" s="914"/>
+      <c r="V3" s="914"/>
+      <c r="W3" s="914"/>
+      <c r="X3" s="914"/>
+      <c r="Y3" s="914"/>
+      <c r="Z3" s="914"/>
+      <c r="AA3" s="914"/>
+      <c r="AB3" s="914"/>
+      <c r="AC3" s="914"/>
       <c r="AD3" s="372"/>
       <c r="AE3" s="373"/>
       <c r="AF3" s="372"/>
-      <c r="AG3" s="919" t="s">
+      <c r="AG3" s="898" t="s">
         <v>206</v>
       </c>
-      <c r="AH3" s="917" t="s">
+      <c r="AH3" s="896" t="s">
         <v>204</v>
       </c>
-      <c r="AI3" s="917" t="s">
+      <c r="AI3" s="896" t="s">
         <v>205</v>
       </c>
-      <c r="AJ3" s="920" t="s">
+      <c r="AJ3" s="899" t="s">
         <v>233</v>
       </c>
       <c r="AK3" s="416"/>
-      <c r="AL3" s="921" t="s">
+      <c r="AL3" s="900" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="921"/>
-      <c r="AN3" s="921"/>
-      <c r="AO3" s="921"/>
+      <c r="AM3" s="900"/>
+      <c r="AN3" s="900"/>
+      <c r="AO3" s="900"/>
     </row>
     <row r="4" spans="1:44" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="374"/>
@@ -13064,40 +13044,40 @@
       <c r="K4" s="372" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="907" t="s">
+      <c r="L4" s="921" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="376" t="s">
         <v>260</v>
       </c>
-      <c r="N4" s="914" t="s">
+      <c r="N4" s="906" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="895" t="s">
+      <c r="O4" s="908" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="895" t="s">
+      <c r="P4" s="908" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="895" t="s">
+      <c r="Q4" s="908" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="895" t="s">
+      <c r="R4" s="908" t="s">
         <v>171</v>
       </c>
-      <c r="S4" s="895" t="s">
+      <c r="S4" s="908" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="895" t="s">
+      <c r="T4" s="908" t="s">
         <v>172</v>
       </c>
-      <c r="U4" s="895" t="s">
+      <c r="U4" s="908" t="s">
         <v>103</v>
       </c>
-      <c r="V4" s="904" t="s">
+      <c r="V4" s="918" t="s">
         <v>236</v>
       </c>
-      <c r="W4" s="895" t="s">
+      <c r="W4" s="908" t="s">
         <v>177</v>
       </c>
       <c r="X4" s="372" t="s">
@@ -13109,28 +13089,28 @@
       <c r="Z4" s="372" t="s">
         <v>98</v>
       </c>
-      <c r="AA4" s="899" t="s">
+      <c r="AA4" s="914" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="901" t="s">
+      <c r="AB4" s="916" t="s">
         <v>69</v>
       </c>
-      <c r="AC4" s="905" t="s">
+      <c r="AC4" s="919" t="s">
         <v>151</v>
       </c>
-      <c r="AD4" s="895" t="s">
+      <c r="AD4" s="908" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="895" t="s">
+      <c r="AE4" s="908" t="s">
         <v>155</v>
       </c>
-      <c r="AF4" s="895" t="s">
+      <c r="AF4" s="908" t="s">
         <v>159</v>
       </c>
-      <c r="AG4" s="919"/>
-      <c r="AH4" s="918"/>
-      <c r="AI4" s="918"/>
-      <c r="AJ4" s="920"/>
+      <c r="AG4" s="898"/>
+      <c r="AH4" s="897"/>
+      <c r="AI4" s="897"/>
+      <c r="AJ4" s="899"/>
       <c r="AK4" s="416"/>
       <c r="AL4" s="378" t="s">
         <v>276</v>
@@ -13179,20 +13159,20 @@
       <c r="K5" s="466" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="908"/>
+      <c r="L5" s="922"/>
       <c r="M5" s="467" t="s">
         <v>261</v>
       </c>
-      <c r="N5" s="915"/>
-      <c r="O5" s="903"/>
-      <c r="P5" s="895"/>
-      <c r="Q5" s="895"/>
-      <c r="R5" s="895"/>
-      <c r="S5" s="903"/>
-      <c r="T5" s="903"/>
-      <c r="U5" s="903"/>
-      <c r="V5" s="904"/>
-      <c r="W5" s="916"/>
+      <c r="N5" s="907"/>
+      <c r="O5" s="909"/>
+      <c r="P5" s="908"/>
+      <c r="Q5" s="908"/>
+      <c r="R5" s="908"/>
+      <c r="S5" s="909"/>
+      <c r="T5" s="909"/>
+      <c r="U5" s="909"/>
+      <c r="V5" s="918"/>
+      <c r="W5" s="910"/>
       <c r="X5" s="372" t="s">
         <v>104</v>
       </c>
@@ -13202,16 +13182,16 @@
       <c r="Z5" s="372" t="s">
         <v>104</v>
       </c>
-      <c r="AA5" s="900"/>
-      <c r="AB5" s="902"/>
-      <c r="AC5" s="905"/>
-      <c r="AD5" s="895"/>
-      <c r="AE5" s="895"/>
-      <c r="AF5" s="896"/>
-      <c r="AG5" s="919"/>
-      <c r="AH5" s="918"/>
-      <c r="AI5" s="918"/>
-      <c r="AJ5" s="920"/>
+      <c r="AA5" s="915"/>
+      <c r="AB5" s="917"/>
+      <c r="AC5" s="919"/>
+      <c r="AD5" s="908"/>
+      <c r="AE5" s="908"/>
+      <c r="AF5" s="911"/>
+      <c r="AG5" s="898"/>
+      <c r="AH5" s="897"/>
+      <c r="AI5" s="897"/>
+      <c r="AJ5" s="899"/>
       <c r="AK5" s="416"/>
       <c r="AL5" s="378" t="s">
         <v>263</v>
@@ -16052,8 +16032,8 @@
     <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B38" s="190"/>
       <c r="G38" s="190"/>
-      <c r="I38" s="909"/>
-      <c r="J38" s="909"/>
+      <c r="I38" s="901"/>
+      <c r="J38" s="901"/>
       <c r="R38" s="190"/>
       <c r="S38" s="190"/>
       <c r="T38" s="190"/>
@@ -16061,8 +16041,8 @@
       <c r="V38" s="190"/>
       <c r="W38" s="190"/>
       <c r="Z38" s="190"/>
-      <c r="AA38" s="910"/>
-      <c r="AB38" s="910"/>
+      <c r="AA38" s="902"/>
+      <c r="AB38" s="902"/>
       <c r="AC38" s="190"/>
       <c r="AD38" s="190"/>
       <c r="AI38" s="380"/>
@@ -17728,19 +17708,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AH3:AH5"/>
-    <mergeCell ref="AG3:AG5"/>
-    <mergeCell ref="AI3:AI5"/>
-    <mergeCell ref="AJ3:AJ5"/>
-    <mergeCell ref="AL3:AO3"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="W4:W5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AD4:AD5"/>
@@ -17757,191 +17724,194 @@
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="AH3:AH5"/>
+    <mergeCell ref="AG3:AG5"/>
+    <mergeCell ref="AI3:AI5"/>
+    <mergeCell ref="AJ3:AJ5"/>
+    <mergeCell ref="AL3:AO3"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="118" priority="9">
+    <cfRule type="expression" dxfId="116" priority="9">
       <formula>B6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B35">
-    <cfRule type="expression" dxfId="117" priority="16">
+    <cfRule type="expression" dxfId="115" priority="16">
       <formula>B7&lt;B6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B12">
-    <cfRule type="expression" dxfId="116" priority="33">
+    <cfRule type="expression" dxfId="114" priority="33">
       <formula>B11&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:D6">
-    <cfRule type="expression" dxfId="115" priority="10">
+    <cfRule type="expression" dxfId="113" priority="10">
       <formula>C6&lt;C5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:D7 H7:J7 R7 T7 W7 AB7">
-    <cfRule type="expression" dxfId="114" priority="20">
+    <cfRule type="expression" dxfId="112" priority="20">
       <formula>C7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D14">
-    <cfRule type="expression" dxfId="113" priority="24">
+    <cfRule type="expression" dxfId="111" priority="24">
       <formula>C8&lt;C7</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C36:D37">
+    <cfRule type="expression" dxfId="110" priority="1088">
+      <formula>C36&lt;C35</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D35 B36:B37">
-    <cfRule type="expression" dxfId="112" priority="1075">
+    <cfRule type="expression" dxfId="109" priority="1075">
       <formula>B35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:D37">
-    <cfRule type="expression" dxfId="111" priority="1088">
-      <formula>C36&lt;C35</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E6:E14">
-    <cfRule type="expression" dxfId="110" priority="3">
+    <cfRule type="expression" dxfId="108" priority="3">
       <formula>E6&lt;E5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E37">
-    <cfRule type="expression" dxfId="109" priority="861">
-      <formula>E36&lt;E35</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F6:F37">
-    <cfRule type="expression" dxfId="108" priority="21">
+    <cfRule type="expression" dxfId="107" priority="21">
       <formula>F6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G37">
-    <cfRule type="expression" dxfId="107" priority="17">
+    <cfRule type="expression" dxfId="106" priority="17">
       <formula>G6&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G36:J37 L36:O37">
+    <cfRule type="expression" dxfId="105" priority="922">
+      <formula>G36&lt;G35</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G6:O6">
-    <cfRule type="expression" dxfId="106" priority="2">
+    <cfRule type="expression" dxfId="104" priority="2">
       <formula>G6&lt;G5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:I34">
-    <cfRule type="expression" dxfId="105" priority="36">
+    <cfRule type="expression" dxfId="103" priority="36">
       <formula>H19&lt;H18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35 R35 T35 W35 AB35 AE35:AI35 P36:P37 S36:S37 X36:Y37">
-    <cfRule type="expression" dxfId="104" priority="1074">
+    <cfRule type="expression" dxfId="102" priority="1074">
       <formula>H35&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:J18">
-    <cfRule type="expression" dxfId="103" priority="25">
+    <cfRule type="expression" dxfId="101" priority="25">
       <formula>H8&lt;H7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J19:J35">
-    <cfRule type="expression" dxfId="102" priority="37">
+    <cfRule type="expression" dxfId="100" priority="37">
       <formula>J19&lt;J18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:L21">
-    <cfRule type="expression" dxfId="101" priority="28">
+    <cfRule type="expression" dxfId="99" priority="28">
       <formula>K9&lt;K8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="100" priority="38">
+    <cfRule type="expression" dxfId="98" priority="38">
       <formula>K22&lt;K21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:O8">
-    <cfRule type="expression" dxfId="99" priority="11">
+    <cfRule type="expression" dxfId="97" priority="11">
       <formula>K7&lt;K6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23:Z23 K24:K37">
-    <cfRule type="expression" dxfId="98" priority="39">
+    <cfRule type="expression" dxfId="96" priority="39">
       <formula>K23&lt;K22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L24:Z27 L28:AC28">
-    <cfRule type="expression" dxfId="97" priority="41">
+    <cfRule type="expression" dxfId="95" priority="41">
       <formula>L24&lt;L23</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:M17">
-    <cfRule type="expression" dxfId="96" priority="30">
+    <cfRule type="expression" dxfId="94" priority="30">
       <formula>M9&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9:O12">
-    <cfRule type="expression" dxfId="95" priority="29">
+    <cfRule type="expression" dxfId="93" priority="29">
       <formula>N9&lt;N8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13:T22">
-    <cfRule type="expression" dxfId="94" priority="32">
+    <cfRule type="expression" dxfId="92" priority="32">
       <formula>N13&lt;N12</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6 X6:Y6 S6:S8">
-    <cfRule type="expression" dxfId="93" priority="8">
+    <cfRule type="expression" dxfId="91" priority="8">
       <formula>P6&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P12 V8:V12">
-    <cfRule type="expression" dxfId="92" priority="27">
+    <cfRule type="expression" dxfId="90" priority="27">
       <formula>P8&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q7">
-    <cfRule type="expression" dxfId="91" priority="18">
+    <cfRule type="expression" dxfId="89" priority="18">
       <formula>P7&lt;P6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36">
-    <cfRule type="expression" dxfId="90" priority="1091">
+    <cfRule type="expression" dxfId="88" priority="1091">
       <formula>Q36&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6:R6 T6:W6 Z6 AB6">
-    <cfRule type="expression" dxfId="89" priority="7">
+    <cfRule type="expression" dxfId="87" priority="7">
       <formula>Q6&lt;Q5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q8:R8">
-    <cfRule type="expression" dxfId="88" priority="26">
+    <cfRule type="expression" dxfId="86" priority="26">
       <formula>Q8&lt;Q7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q9:T12">
-    <cfRule type="expression" dxfId="87" priority="31">
+    <cfRule type="expression" dxfId="85" priority="31">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36">
-    <cfRule type="expression" dxfId="86" priority="1087">
+    <cfRule type="expression" dxfId="84" priority="1087">
       <formula>R36&lt;R35</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L36:O37 G36:J37">
-    <cfRule type="expression" dxfId="85" priority="922">
-      <formula>G36&lt;G35</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T8 AB8:AC8 AE8:AI8 AB9:AI27">
-    <cfRule type="expression" dxfId="84" priority="22">
+    <cfRule type="expression" dxfId="83" priority="22">
       <formula>T8&lt;T7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U22">
-    <cfRule type="expression" dxfId="83" priority="5">
+    <cfRule type="expression" dxfId="82" priority="5">
       <formula>U6&lt;U5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U36:V37 U35">
-    <cfRule type="expression" dxfId="82" priority="988">
-      <formula>U35&lt;U34</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V7">
@@ -17949,7 +17919,7 @@
       <formula>V7&lt;V6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V13:X14 C15:E34 C35 E35">
+  <conditionalFormatting sqref="V13:X14 C15:E34 C35 E35:E37">
     <cfRule type="expression" dxfId="80" priority="35">
       <formula>C13&lt;C12</formula>
     </cfRule>
@@ -17959,7 +17929,7 @@
       <formula>M15&lt;M14</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 Z32:AB34 V35 X35:AA35 AC31:AC37">
+  <conditionalFormatting sqref="V29:AC29 AA30:AC30 Z30:Z31 V30:Y34 AA31:AB31 AC31:AC37 Z32:AB34 V35 X35:AA35">
     <cfRule type="expression" dxfId="78" priority="45">
       <formula>V29&lt;V28</formula>
     </cfRule>
@@ -18009,7 +17979,7 @@
       <formula>X7&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE28:AI34 L29:T34 L35:Q35 S35 U29:U37">
+  <conditionalFormatting sqref="AE28:AI34 L29:T34 U29:U37 L35:Q35 S35">
     <cfRule type="expression" dxfId="68" priority="44">
       <formula>L28&lt;L27</formula>
     </cfRule>
@@ -18029,7 +17999,7 @@
       <formula>AK13&lt;#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 Z36:Z37 T36:T37 W36:W37 AB36:AB37 AE36:AI37 Q37:R37">
+  <conditionalFormatting sqref="AL9:AL14 AL15:AN34 AK16:AK37 AK20:AN21 T36:W37 Z36:Z37 AB36:AB37 AE36:AI37 Q37:R37">
     <cfRule type="expression" dxfId="64" priority="981">
       <formula>Q9&lt;Q8</formula>
     </cfRule>
@@ -18335,7 +18305,7 @@
         <v>31</v>
       </c>
       <c r="AG6" s="293"/>
-      <c r="AH6" s="893" t="s">
+      <c r="AH6" s="894" t="s">
         <v>216</v>
       </c>
       <c r="AI6" s="291"/>
@@ -18440,7 +18410,7 @@
       <c r="AG7" s="212" t="s">
         <v>19</v>
       </c>
-      <c r="AH7" s="893"/>
+      <c r="AH7" s="894"/>
       <c r="AI7" s="292" t="s">
         <v>229</v>
       </c>
@@ -18805,11 +18775,11 @@
         <f>'Daily KPIs'!X10</f>
         <v>ST/CBex</v>
       </c>
-      <c r="Y10" s="1021" t="str">
+      <c r="Y10" s="1022" t="str">
         <f>'Daily KPIs'!Y10</f>
         <v>CBex</v>
       </c>
-      <c r="Z10" s="1021"/>
+      <c r="Z10" s="1022"/>
       <c r="AA10" s="163">
         <f>'Daily KPIs'!AA10</f>
         <v>0</v>
@@ -23626,28 +23596,28 @@
         <f t="shared" si="13"/>
         <v>3.8053949903660889</v>
       </c>
-      <c r="AD63" s="168" t="str">
+      <c r="AD63" s="168">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AE63" s="168" t="str">
+        <v>1.9055077003393368</v>
+      </c>
+      <c r="AE63" s="168">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AF63" s="168" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="168">
         <f t="shared" si="13"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG63" s="243">
         <f>IF(+(AG28*10)/AG$93&lt;1,0,+(AG28*10)/AG$93)</f>
-        <v>5.1964512040557675</v>
+        <v>4.2879340225900915</v>
       </c>
       <c r="AH63" s="243">
         <v>2.5</v>
       </c>
       <c r="AI63" s="244">
         <f t="shared" si="11"/>
-        <v>-2.6964512040557675</v>
+        <v>-1.7879340225900915</v>
       </c>
     </row>
     <row r="64" spans="1:37" s="90" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -25421,7 +25391,7 @@
       </c>
       <c r="AD78" s="152">
         <f>SUM(AD62:AD77)</f>
-        <v>0</v>
+        <v>1.9055077003393368</v>
       </c>
       <c r="AE78" s="152">
         <f>SUM(AE62:AE77)</f>
@@ -25433,7 +25403,7 @@
       </c>
       <c r="AG78" s="253">
         <f>SUM(AG62:AG77)</f>
-        <v>13.856840129148384</v>
+        <v>12.948322947682708</v>
       </c>
       <c r="AH78" s="253">
         <f t="shared" si="37"/>
@@ -25441,7 +25411,7 @@
       </c>
       <c r="AI78" s="253">
         <f t="shared" si="11"/>
-        <v>1.7431598708516134</v>
+        <v>2.6516770523172895</v>
       </c>
       <c r="AJ78" s="210"/>
       <c r="AK78" s="210"/>
@@ -27023,19 +26993,19 @@
       </c>
       <c r="AD93" s="165">
         <f>'Daily KPIs'!AD12</f>
-        <v>0</v>
+        <v>383.1</v>
       </c>
       <c r="AE93" s="165">
         <f>'Daily KPIs'!AE12</f>
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="AF93" s="208">
         <f>'Daily KPIs'!AD12</f>
-        <v>0</v>
+        <v>383.1</v>
       </c>
       <c r="AG93" s="260">
         <f>SUM(B93:AF93)</f>
-        <v>5522.9999999999991</v>
+        <v>6693.2</v>
       </c>
       <c r="AH93" s="261"/>
       <c r="AI93" s="289"/>
@@ -27160,9 +27130,9 @@
         <f>'Daily KPIs'!AD13</f>
         <v>VM</v>
       </c>
-      <c r="AE94" s="166">
+      <c r="AE94" s="166" t="str">
         <f>'Daily KPIs'!AE13</f>
-        <v>0</v>
+        <v>ST</v>
       </c>
       <c r="AF94" s="209" t="str">
         <f>'Daily KPIs'!AD13</f>
@@ -27294,7 +27264,7 @@
       </c>
       <c r="AE95" s="174">
         <f>'Daily KPIs'!AE14</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF95" s="206">
         <f>'Daily KPIs'!AD14</f>
@@ -27302,7 +27272,7 @@
       </c>
       <c r="AG95" s="262">
         <f>SUM($B95:AF95)</f>
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AH95" s="262"/>
       <c r="AI95" s="290"/>
@@ -27956,8 +27926,8 @@
       </c>
       <c r="B3" s="469"/>
       <c r="C3" s="469"/>
-      <c r="K3" s="894"/>
-      <c r="L3" s="894"/>
+      <c r="K3" s="895"/>
+      <c r="L3" s="895"/>
       <c r="M3" s="499"/>
       <c r="AH3" s="291"/>
       <c r="AI3" s="291"/>
@@ -28103,7 +28073,7 @@
         <v>1</v>
       </c>
       <c r="AG6" s="291"/>
-      <c r="AI6" s="893" t="s">
+      <c r="AI6" s="894" t="s">
         <v>216</v>
       </c>
     </row>
@@ -28206,7 +28176,7 @@
       <c r="AH7" s="478" t="s">
         <v>19</v>
       </c>
-      <c r="AI7" s="893"/>
+      <c r="AI7" s="894"/>
       <c r="AJ7" s="292" t="s">
         <v>229</v>
       </c>
@@ -28322,19 +28292,22 @@
         <f>1337+3422</f>
         <v>4759</v>
       </c>
-      <c r="AE8" s="679"/>
+      <c r="AE8" s="679">
+        <f>3376+1423</f>
+        <v>4799</v>
+      </c>
       <c r="AF8" s="679"/>
       <c r="AG8" s="748"/>
       <c r="AH8" s="481">
         <f>SUM(B8:AG8)</f>
-        <v>105766</v>
+        <v>110565</v>
       </c>
       <c r="AI8" s="527">
         <v>114150</v>
       </c>
       <c r="AJ8" s="294">
         <f>AH8-AI8</f>
-        <v>-8384</v>
+        <v>-3585</v>
       </c>
       <c r="AK8" s="482"/>
       <c r="AL8" s="482"/>
@@ -28470,13 +28443,13 @@
       </c>
       <c r="AE9" s="679">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>316.73400000000004</v>
       </c>
       <c r="AF9" s="679"/>
       <c r="AG9" s="749"/>
       <c r="AH9" s="485">
         <f>SUM(B9:AG9)</f>
-        <v>6980.5560000000014</v>
+        <v>7297.2900000000018</v>
       </c>
       <c r="AI9" s="485"/>
       <c r="AL9" s="291" t="s">
@@ -28812,13 +28785,17 @@
       <c r="AC12" s="495">
         <v>415.2</v>
       </c>
-      <c r="AD12" s="495"/>
-      <c r="AE12" s="495"/>
+      <c r="AD12" s="495">
+        <v>383.1</v>
+      </c>
+      <c r="AE12" s="495">
+        <v>404</v>
+      </c>
       <c r="AF12" s="495"/>
       <c r="AG12" s="495"/>
       <c r="AH12" s="496">
         <f>SUM(B12:AF12)</f>
-        <v>5522.9999999999991</v>
+        <v>6310.0999999999995</v>
       </c>
       <c r="AI12" s="497"/>
       <c r="AJ12" s="470"/>
@@ -28898,10 +28875,12 @@
       <c r="AC13" s="885" t="s">
         <v>326</v>
       </c>
-      <c r="AD13" s="1022" t="s">
+      <c r="AD13" s="893" t="s">
         <v>328</v>
       </c>
-      <c r="AE13" s="683"/>
+      <c r="AE13" s="683" t="s">
+        <v>310</v>
+      </c>
       <c r="AF13" s="683"/>
       <c r="AG13" s="686"/>
       <c r="AH13" s="497"/>
@@ -28992,12 +28971,14 @@
       <c r="AD14" s="499">
         <v>8</v>
       </c>
-      <c r="AE14" s="499"/>
+      <c r="AE14" s="499">
+        <v>8</v>
+      </c>
       <c r="AF14" s="499"/>
       <c r="AG14" s="499"/>
       <c r="AH14" s="469">
         <f>SUM(B14:AF14)</f>
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:149" s="505" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29038,7 +29019,7 @@
       <c r="AG15" s="719"/>
       <c r="AH15" s="501">
         <f>IF(AH12=0,"",+(AH36*10)/AH12)</f>
-        <v>5.3521636791598777</v>
+        <v>4.6845533351293964</v>
       </c>
       <c r="AI15" s="503"/>
       <c r="AJ15" s="504"/>
@@ -30142,7 +30123,7 @@
       </c>
       <c r="AK26" s="525">
         <f>(AI26*10)/AH9</f>
-        <v>11.81997537158931</v>
+        <v>11.306937232863156</v>
       </c>
     </row>
     <row r="27" spans="1:149" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -33811,9 +33792,9 @@
         <f t="shared" si="10"/>
         <v>5.0621788381822004</v>
       </c>
-      <c r="AE54" s="546" t="str">
+      <c r="AE54" s="546">
         <f t="shared" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF54" s="546" t="str">
         <f t="shared" si="10"/>
@@ -33822,14 +33803,14 @@
       <c r="AG54" s="546"/>
       <c r="AH54" s="547">
         <f>+(AH36*10)/AH$9</f>
-        <v>4.2346197065104834</v>
+        <v>4.0508188656336799</v>
       </c>
       <c r="AI54" s="547">
         <v>3.2</v>
       </c>
       <c r="AJ54" s="548">
         <f t="shared" ref="AJ54:AJ67" si="11">AI54-AH54</f>
-        <v>-1.0346197065104832</v>
+        <v>-0.8508188656336797</v>
       </c>
     </row>
     <row r="55" spans="1:59" s="554" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -34023,9 +34004,9 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AE56" s="546" t="str">
+      <c r="AE56" s="546">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF56" s="546" t="str">
         <f t="shared" si="16"/>
@@ -34100,7 +34081,7 @@
         <v/>
       </c>
       <c r="I57" s="550">
-        <f t="shared" ref="I57:AF57" si="19">IF(I$9=0,"",+(I39*10)/I$9)</f>
+        <f t="shared" ref="I57:AE57" si="19">IF(I$9=0,"",+(I39*10)/I$9)</f>
         <v>0</v>
       </c>
       <c r="J57" s="550">
@@ -34187,9 +34168,9 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AE57" s="550" t="str">
+      <c r="AE57" s="550">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF57" s="550" t="str">
         <f>IF(AF$9=0,"",+(AF39*10)/AF$9)</f>
@@ -34351,9 +34332,9 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AE58" s="546" t="str">
+      <c r="AE58" s="546">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF58" s="546" t="str">
         <f t="shared" si="20"/>
@@ -34517,9 +34498,9 @@
         <f t="shared" si="21"/>
         <v>1.1143160964552012</v>
       </c>
-      <c r="AE59" s="550" t="str">
+      <c r="AE59" s="550">
         <f t="shared" si="21"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF59" s="550" t="str">
         <f t="shared" si="21"/>
@@ -34528,14 +34509,14 @@
       <c r="AG59" s="550"/>
       <c r="AH59" s="550">
         <f t="shared" si="12"/>
-        <v>1.3766811698093959</v>
+        <v>1.3169272428531684</v>
       </c>
       <c r="AI59" s="551">
         <v>0.7</v>
       </c>
       <c r="AJ59" s="552">
         <f t="shared" si="11"/>
-        <v>-0.67668116980939597</v>
+        <v>-0.61692724285316847</v>
       </c>
       <c r="AK59" s="475"/>
       <c r="AL59" s="475"/>
@@ -34681,9 +34662,9 @@
         <f t="shared" si="22"/>
         <v>3.0564098645628381</v>
       </c>
-      <c r="AE60" s="546" t="str">
+      <c r="AE60" s="546">
         <f t="shared" si="22"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF60" s="546" t="str">
         <f t="shared" si="22"/>
@@ -34692,14 +34673,14 @@
       <c r="AG60" s="546"/>
       <c r="AH60" s="569">
         <f t="shared" si="12"/>
-        <v>2.9252684170143461</v>
+        <v>2.7982990945953903</v>
       </c>
       <c r="AI60" s="556">
         <v>2.1</v>
       </c>
       <c r="AJ60" s="548">
         <f t="shared" si="11"/>
-        <v>-0.82526841701434606</v>
+        <v>-0.69829909459539019</v>
       </c>
     </row>
     <row r="61" spans="1:59" s="505" customFormat="1" x14ac:dyDescent="0.35">
@@ -34822,9 +34803,9 @@
         <f t="shared" si="23"/>
         <v>0.47756404133794345</v>
       </c>
-      <c r="AE61" s="550" t="str">
+      <c r="AE61" s="550">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF61" s="550" t="str">
         <f t="shared" si="23"/>
@@ -34833,14 +34814,14 @@
       <c r="AG61" s="550"/>
       <c r="AH61" s="551">
         <f t="shared" si="12"/>
-        <v>0.50425782702695876</v>
+        <v>0.48237085274122299</v>
       </c>
       <c r="AI61" s="551">
         <v>0.7</v>
       </c>
       <c r="AJ61" s="552">
         <f t="shared" si="11"/>
-        <v>0.1957421729730412</v>
+        <v>0.21762914725877697</v>
       </c>
       <c r="AK61" s="475"/>
       <c r="AL61" s="475"/>
@@ -34986,9 +34967,9 @@
         <f t="shared" si="24"/>
         <v>6.3675205511725785E-2</v>
       </c>
-      <c r="AE62" s="546" t="str">
+      <c r="AE62" s="546">
         <f t="shared" si="24"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF62" s="546" t="str">
         <f t="shared" si="24"/>
@@ -34997,14 +34978,14 @@
       <c r="AG62" s="546"/>
       <c r="AH62" s="556">
         <f>+(AH44*10)/AH$9</f>
-        <v>9.3115791922591826E-2</v>
+        <v>8.9074163148237198E-2</v>
       </c>
       <c r="AI62" s="556">
         <v>0.1</v>
       </c>
       <c r="AJ62" s="548">
         <f t="shared" si="11"/>
-        <v>6.8842080774081799E-3</v>
+        <v>1.0925836851762807E-2</v>
       </c>
     </row>
     <row r="63" spans="1:59" s="505" customFormat="1" x14ac:dyDescent="0.35">
@@ -35127,9 +35108,9 @@
         <f t="shared" si="25"/>
         <v>0.79594006889657243</v>
       </c>
-      <c r="AE63" s="550" t="str">
+      <c r="AE63" s="550">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF63" s="550" t="str">
         <f t="shared" si="25"/>
@@ -35138,14 +35119,14 @@
       <c r="AG63" s="550"/>
       <c r="AH63" s="551">
         <f>+(AH45*10)/AH$9</f>
-        <v>0.59594106830458771</v>
+        <v>0.57007464414871811</v>
       </c>
       <c r="AI63" s="551">
         <v>0.6</v>
       </c>
       <c r="AJ63" s="552">
         <f t="shared" si="11"/>
-        <v>4.0589316954122712E-3</v>
+        <v>2.9925355851281865E-2</v>
       </c>
       <c r="AK63" s="475"/>
       <c r="AL63" s="475"/>
@@ -35359,9 +35340,9 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AE65" s="576" t="str">
+      <c r="AE65" s="576">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF65" s="576" t="str">
         <f t="shared" si="26"/>
@@ -35670,7 +35651,7 @@
       <c r="AG68" s="586"/>
       <c r="AH68" s="585">
         <f t="shared" si="27"/>
-        <v>9.7298839805883635</v>
+        <v>9.3075648631204153</v>
       </c>
       <c r="AI68" s="585">
         <f>SUM(AI54:AI63,AI65)</f>
@@ -35678,7 +35659,7 @@
       </c>
       <c r="AJ68" s="548">
         <f t="shared" si="27"/>
-        <v>-0.12988398058836365</v>
+        <v>0.29243513687958317</v>
       </c>
       <c r="AK68" s="469"/>
       <c r="AL68" s="291"/>
@@ -35835,7 +35816,7 @@
       <c r="AG69" s="589"/>
       <c r="AH69" s="588">
         <f t="shared" si="28"/>
-        <v>3.522642035963897</v>
+        <v>3.3697441104848505</v>
       </c>
       <c r="AI69" s="588">
         <f t="shared" si="28"/>
@@ -35843,7 +35824,7 @@
       </c>
       <c r="AJ69" s="588">
         <f t="shared" si="28"/>
-        <v>-0.62264203596389667</v>
+        <v>-0.46974411048485043</v>
       </c>
       <c r="AK69" s="590"/>
       <c r="AL69" s="291"/>
@@ -36231,7 +36212,7 @@
         <v>1200</v>
       </c>
       <c r="AE74" s="884">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="AF74" s="884">
         <v>0</v>
@@ -36239,7 +36220,7 @@
       <c r="AG74" s="795"/>
       <c r="AH74" s="517">
         <f>SUM(B74:AF74)</f>
-        <v>36900</v>
+        <v>38500</v>
       </c>
       <c r="AI74" s="538"/>
       <c r="AJ74" s="538"/>
@@ -37999,9 +37980,9 @@
         <f t="shared" si="33"/>
         <v>10.092520073608538</v>
       </c>
-      <c r="AE90" s="654" t="str">
+      <c r="AE90" s="654">
         <f>IF(AE$9=0,"",+(AE22*10)/AE$9)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF90" s="655" t="str">
         <f t="shared" si="33"/>
@@ -38010,18 +37991,18 @@
       <c r="AG90" s="628"/>
       <c r="AH90" s="660">
         <f>IF(AH$9=0,"0",+(AH22*10)/AH$9)</f>
-        <v>12.318502996036417</v>
+        <v>11.783826598641411</v>
       </c>
       <c r="AI90" s="663">
         <v>10.199999999999999</v>
       </c>
       <c r="AJ90" s="666">
         <f>+AI90-AH90</f>
-        <v>-2.1185029960364172</v>
+        <v>-1.5838265986414122</v>
       </c>
       <c r="AK90" s="668">
         <f>AH90/AI90*100</f>
-        <v>120.76963721604331</v>
+        <v>115.52771175138639</v>
       </c>
       <c r="AL90" s="630"/>
       <c r="AM90" s="631"/>
@@ -38233,9 +38214,9 @@
         <f t="shared" si="35"/>
         <v>3.8205123307035476</v>
       </c>
-      <c r="AE92" s="654" t="str">
+      <c r="AE92" s="654">
         <f t="shared" si="35"/>
-        <v/>
+        <v>5.0515574583088645</v>
       </c>
       <c r="AF92" s="654" t="str">
         <f t="shared" si="35"/>
@@ -38244,18 +38225,18 @@
       <c r="AG92" s="629"/>
       <c r="AH92" s="671">
         <f>IF(AH$9=0,"0",+(AH74)/AH$9)</f>
-        <v>5.2861118799132898</v>
+        <v>5.2759312018571265</v>
       </c>
       <c r="AI92" s="675">
         <v>5</v>
       </c>
       <c r="AJ92" s="676">
         <f>AI92-AH92</f>
-        <v>-0.28611187991328979</v>
+        <v>-0.2759312018571265</v>
       </c>
       <c r="AK92" s="674">
         <f t="shared" si="34"/>
-        <v>105.72223759826581</v>
+        <v>105.51862403714254</v>
       </c>
       <c r="AL92" s="630"/>
       <c r="AM92" s="631"/>
@@ -38402,9 +38383,9 @@
         <f t="shared" si="36"/>
         <v>0.57925334454017696</v>
       </c>
-      <c r="AE93" s="654" t="str">
+      <c r="AE93" s="654">
         <f t="shared" si="36"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF93" s="654" t="str">
         <f t="shared" si="36"/>
@@ -38413,18 +38394,18 @@
       <c r="AG93" s="629"/>
       <c r="AH93" s="671">
         <f>IF(AH$9=0,"0",+AH76/AH$9)</f>
-        <v>0.58042654481964051</v>
+        <v>0.55523351819648259</v>
       </c>
       <c r="AI93" s="675">
         <v>1.7</v>
       </c>
       <c r="AJ93" s="677">
         <f>AI93-AH93</f>
-        <v>1.1195734551803596</v>
+        <v>1.1447664818035173</v>
       </c>
       <c r="AK93" s="674">
         <f t="shared" si="34"/>
-        <v>34.142737930567094</v>
+        <v>32.660795188028388</v>
       </c>
       <c r="AL93" s="636"/>
       <c r="AM93" s="637"/>
@@ -38569,9 +38550,9 @@
         <f t="shared" si="37"/>
         <v>26.947028596534796</v>
       </c>
-      <c r="AE94" s="654" t="str">
+      <c r="AE94" s="654">
         <f t="shared" si="37"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF94" s="654" t="str">
         <f t="shared" si="37"/>
@@ -38580,18 +38561,18 @@
       <c r="AG94" s="628"/>
       <c r="AH94" s="671">
         <f>IF(AH$9=0,"0",+(AH80+AH83)/AH$9)</f>
-        <v>31.560165121517535</v>
+        <v>30.190317227354257</v>
       </c>
       <c r="AI94" s="675">
         <v>22</v>
       </c>
       <c r="AJ94" s="676">
         <f>AI94-AH94</f>
-        <v>-9.5601651215175352</v>
+        <v>-8.1903172273542566</v>
       </c>
       <c r="AK94" s="674">
         <f>AH94/AI94*100</f>
-        <v>143.45529600689787</v>
+        <v>137.22871466979208</v>
       </c>
       <c r="AL94" s="630"/>
       <c r="AM94" s="631"/>
@@ -38651,7 +38632,7 @@
       <c r="AG95" s="638"/>
       <c r="AH95" s="671">
         <f>IF(AH$9=0,"0",+(AH78*10)/AH$9)</f>
-        <v>31.415019090169942</v>
+        <v>30.051471162582317</v>
       </c>
       <c r="AI95" s="675"/>
       <c r="AJ95" s="677"/>
@@ -38802,9 +38783,9 @@
         <f t="shared" si="39"/>
         <v>9.4876056212471429</v>
       </c>
-      <c r="AE96" s="655" t="str">
+      <c r="AE96" s="655">
         <f t="shared" si="39"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF96" s="655" t="str">
         <f>IF(AF$9=0,"",AF84/AF$9)</f>
@@ -38813,18 +38794,18 @@
       <c r="AG96" s="628"/>
       <c r="AH96" s="661">
         <f>IF(AH$9=0,"0",+(AH84)/AH$9)</f>
-        <v>9.5078386306191067</v>
+        <v>9.0951572433053887</v>
       </c>
       <c r="AI96" s="664">
         <v>7.2</v>
       </c>
       <c r="AJ96" s="678">
         <f>AI96-AH96</f>
-        <v>-2.3078386306191065</v>
+        <v>-1.8951572433053885</v>
       </c>
       <c r="AK96" s="669">
         <f t="shared" si="34"/>
-        <v>132.05331431415425</v>
+        <v>126.3216283792415</v>
       </c>
       <c r="AL96" s="630"/>
       <c r="AM96" s="631"/>
@@ -42573,24 +42554,24 @@
     </row>
     <row r="6" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="922" t="s">
+      <c r="A7" s="923" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="383"/>
       <c r="C7" s="383"/>
-      <c r="D7" s="935" t="s">
+      <c r="D7" s="936" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="938" t="s">
+      <c r="E7" s="939" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="932" t="s">
+      <c r="F7" s="933" t="s">
         <v>287</v>
       </c>
-      <c r="G7" s="928" t="s">
+      <c r="G7" s="929" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="928" t="s">
+      <c r="H7" s="929" t="s">
         <v>256</v>
       </c>
       <c r="I7" s="383" t="s">
@@ -42602,33 +42583,33 @@
       <c r="K7" s="390" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="929" t="s">
+      <c r="L7" s="930" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="930"/>
-      <c r="N7" s="930"/>
-      <c r="O7" s="930"/>
-      <c r="P7" s="931"/>
-      <c r="Q7" s="926" t="s">
+      <c r="M7" s="931"/>
+      <c r="N7" s="931"/>
+      <c r="O7" s="931"/>
+      <c r="P7" s="932"/>
+      <c r="Q7" s="927" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="927"/>
-      <c r="S7" s="927"/>
-      <c r="T7" s="927"/>
+      <c r="R7" s="928"/>
+      <c r="S7" s="928"/>
+      <c r="T7" s="928"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="923"/>
+      <c r="A8" s="924"/>
       <c r="B8" s="384" t="s">
         <v>257</v>
       </c>
       <c r="C8" s="384" t="s">
         <v>258</v>
       </c>
-      <c r="D8" s="936"/>
-      <c r="E8" s="939"/>
-      <c r="F8" s="933"/>
-      <c r="G8" s="928"/>
-      <c r="H8" s="928"/>
+      <c r="D8" s="937"/>
+      <c r="E8" s="940"/>
+      <c r="F8" s="934"/>
+      <c r="G8" s="929"/>
+      <c r="H8" s="929"/>
       <c r="I8" s="383"/>
       <c r="J8" s="383"/>
       <c r="K8" s="390"/>
@@ -42651,12 +42632,12 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="924"/>
+      <c r="A9" s="925"/>
       <c r="B9" s="385"/>
       <c r="C9" s="385"/>
-      <c r="D9" s="937"/>
-      <c r="E9" s="940"/>
-      <c r="F9" s="934"/>
+      <c r="D9" s="938"/>
+      <c r="E9" s="941"/>
+      <c r="F9" s="935"/>
       <c r="G9" s="383" t="s">
         <v>56</v>
       </c>
@@ -45037,7 +45018,7 @@
       </c>
       <c r="K39" s="723">
         <f>'CO2'!E36</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="L39" s="724">
         <f>+'PROD.FIG. '!F34</f>
@@ -45056,7 +45037,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="725">
-        <v>0</v>
+        <v>316.73400000000004</v>
       </c>
       <c r="Q39" s="393">
         <f t="shared" si="3"/>
@@ -45255,7 +45236,7 @@
       </c>
       <c r="K43" s="20">
         <f t="shared" si="7"/>
-        <v>35803</v>
+        <v>37403</v>
       </c>
       <c r="L43" s="20">
         <f t="shared" si="7"/>
@@ -45275,7 +45256,7 @@
       </c>
       <c r="P43" s="403">
         <f t="shared" si="7"/>
-        <v>6980.5560000000014</v>
+        <v>7297.2900000000018</v>
       </c>
       <c r="Q43" s="408" t="s">
         <v>13</v>
@@ -45318,19 +45299,19 @@
       <c r="P44" s="401"/>
       <c r="Q44" s="397">
         <f>IF(P43=0,0,H43/P43)</f>
-        <v>30.419145695557766</v>
+        <v>29.098822987711866</v>
       </c>
       <c r="R44" s="398">
         <f>IF(Q44=0,0,I43/P43)</f>
-        <v>12.080842844037063</v>
+        <v>11.556481926852294</v>
       </c>
       <c r="S44" s="398">
         <f>IF(R44=0,0,J43/P43)</f>
-        <v>9.107002364854603</v>
+        <v>8.7117190080153026</v>
       </c>
       <c r="T44" s="399">
         <f>IF(S44=0,0,K43/P43)</f>
-        <v>5.1289610741608538</v>
+        <v>5.1256014218977173</v>
       </c>
     </row>
     <row r="45" spans="1:32" ht="15" x14ac:dyDescent="0.2">
@@ -45363,12 +45344,12 @@
       <c r="T46" s="2"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="D47" s="925"/>
-      <c r="E47" s="925"/>
-      <c r="F47" s="925"/>
-      <c r="G47" s="925"/>
-      <c r="H47" s="925"/>
-      <c r="I47" s="925"/>
+      <c r="D47" s="926"/>
+      <c r="E47" s="926"/>
+      <c r="F47" s="926"/>
+      <c r="G47" s="926"/>
+      <c r="H47" s="926"/>
+      <c r="I47" s="926"/>
       <c r="AF47" t="s">
         <v>55</v>
       </c>
@@ -45482,16 +45463,16 @@
       <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="941" t="s">
+      <c r="A3" s="942" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="943" t="s">
+      <c r="B3" s="944" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="942"/>
-      <c r="B4" s="944"/>
+      <c r="A4" s="943"/>
+      <c r="B4" s="945"/>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="36">
@@ -45855,31 +45836,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="953" t="s">
+      <c r="A1" s="954" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="954"/>
-      <c r="C1" s="954"/>
-      <c r="D1" s="954"/>
-      <c r="E1" s="954"/>
-      <c r="F1" s="954"/>
-      <c r="G1" s="954"/>
-      <c r="H1" s="954"/>
-      <c r="I1" s="954"/>
-      <c r="J1" s="954"/>
-      <c r="K1" s="954"/>
-      <c r="L1" s="954"/>
-      <c r="M1" s="954"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
+      <c r="I1" s="955"/>
+      <c r="J1" s="955"/>
+      <c r="K1" s="955"/>
+      <c r="L1" s="955"/>
+      <c r="M1" s="955"/>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
-      <c r="M2" s="945" t="s">
+      <c r="M2" s="946" t="s">
         <v>303</v>
       </c>
-      <c r="N2" s="945" t="s">
+      <c r="N2" s="946" t="s">
         <v>304</v>
       </c>
     </row>
@@ -45888,11 +45869,11 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="M3" s="946"/>
-      <c r="N3" s="946"/>
+      <c r="M3" s="947"/>
+      <c r="N3" s="947"/>
     </row>
     <row r="4" spans="1:17" s="339" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="959" t="s">
+      <c r="A4" s="960" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="852" t="s">
@@ -45925,22 +45906,22 @@
       <c r="K4" s="853" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="955" t="s">
+      <c r="L4" s="956" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="957" t="s">
+      <c r="M4" s="958" t="s">
         <v>246</v>
       </c>
-      <c r="N4" s="947" t="s">
+      <c r="N4" s="948" t="s">
         <v>246</v>
       </c>
-      <c r="O4" s="950" t="s">
+      <c r="O4" s="951" t="s">
         <v>306</v>
       </c>
       <c r="P4" s="350"/>
     </row>
     <row r="5" spans="1:17" s="339" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="960"/>
+      <c r="A5" s="961"/>
       <c r="B5" s="869" t="s">
         <v>41</v>
       </c>
@@ -45971,10 +45952,10 @@
       <c r="K5" s="870" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="956"/>
-      <c r="M5" s="958"/>
-      <c r="N5" s="948"/>
-      <c r="O5" s="951"/>
+      <c r="L5" s="957"/>
+      <c r="M5" s="959"/>
+      <c r="N5" s="949"/>
+      <c r="O5" s="952"/>
       <c r="P5" s="350"/>
     </row>
     <row r="6" spans="1:17" s="73" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -45991,8 +45972,8 @@
       <c r="K6" s="841"/>
       <c r="L6" s="874"/>
       <c r="M6" s="838"/>
-      <c r="N6" s="949"/>
-      <c r="O6" s="952"/>
+      <c r="N6" s="950"/>
+      <c r="O6" s="953"/>
       <c r="P6" s="350"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -47632,14 +47613,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="836" t="str">
-        <v>0</v>
-      </c>
-      <c r="M36" s="834" t="str">
+      <c r="L36" s="836">
+        <v>316.73400000000004</v>
+      </c>
+      <c r="M36" s="834">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N36" s="834" t="str">
+      <c r="N36" s="834">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -47740,15 +47721,15 @@
       </c>
       <c r="L38" s="833">
         <f>SUM(L7:L37)</f>
-        <v>6980.5560000000014</v>
+        <v>7297.2900000000018</v>
       </c>
       <c r="M38" s="839">
         <f>IF(L38=0,"0",(K38/L38))</f>
-        <v>9.5078386306191067</v>
+        <v>9.0951572433053887</v>
       </c>
       <c r="N38" s="839">
         <f>IF(L38=0,"0",(D38/L38))</f>
-        <v>8.9034741645221303</v>
+        <v>8.5170248133211004</v>
       </c>
       <c r="O38" s="840"/>
     </row>
@@ -48446,115 +48427,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="953"/>
-      <c r="B1" s="954"/>
-      <c r="C1" s="954"/>
-      <c r="D1" s="954"/>
-      <c r="E1" s="954"/>
-      <c r="F1" s="954"/>
-      <c r="G1" s="954"/>
-      <c r="H1" s="954"/>
-      <c r="I1" s="954"/>
-      <c r="J1" s="954"/>
-      <c r="K1" s="954"/>
-      <c r="L1" s="954"/>
-      <c r="M1" s="954"/>
-      <c r="N1" s="954"/>
-      <c r="O1" s="954"/>
-      <c r="P1" s="954"/>
-      <c r="Q1" s="954"/>
-      <c r="R1" s="954"/>
-      <c r="S1" s="954"/>
-      <c r="T1" s="954"/>
-      <c r="U1" s="954"/>
-      <c r="V1" s="954"/>
-      <c r="W1" s="954"/>
-      <c r="X1" s="954"/>
-      <c r="Y1" s="954"/>
-      <c r="Z1" s="954"/>
-      <c r="AA1" s="954"/>
+      <c r="A1" s="954"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
+      <c r="I1" s="955"/>
+      <c r="J1" s="955"/>
+      <c r="K1" s="955"/>
+      <c r="L1" s="955"/>
+      <c r="M1" s="955"/>
+      <c r="N1" s="955"/>
+      <c r="O1" s="955"/>
+      <c r="P1" s="955"/>
+      <c r="Q1" s="955"/>
+      <c r="R1" s="955"/>
+      <c r="S1" s="955"/>
+      <c r="T1" s="955"/>
+      <c r="U1" s="955"/>
+      <c r="V1" s="955"/>
+      <c r="W1" s="955"/>
+      <c r="X1" s="955"/>
+      <c r="Y1" s="955"/>
+      <c r="Z1" s="955"/>
+      <c r="AA1" s="955"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:31" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="965" t="s">
+      <c r="B4" s="974" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="963" t="s">
+      <c r="C4" s="966" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="961" t="s">
+      <c r="D4" s="971" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="963" t="s">
+      <c r="E4" s="966" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="961" t="s">
+      <c r="F4" s="971" t="s">
         <v>239</v>
       </c>
-      <c r="G4" s="961" t="s">
+      <c r="G4" s="971" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="961" t="s">
+      <c r="H4" s="971" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="963" t="s">
+      <c r="I4" s="966" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="963" t="s">
+      <c r="J4" s="966" t="s">
         <v>109</v>
       </c>
-      <c r="K4" s="963" t="s">
+      <c r="K4" s="966" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="963" t="s">
+      <c r="L4" s="966" t="s">
         <v>173</v>
       </c>
-      <c r="M4" s="963" t="s">
+      <c r="M4" s="966" t="s">
         <v>103</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
-      <c r="R4" s="961" t="s">
+      <c r="R4" s="971" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="961" t="s">
+      <c r="S4" s="971" t="s">
         <v>240</v>
       </c>
       <c r="T4" s="48"/>
-      <c r="U4" s="963" t="s">
+      <c r="U4" s="966" t="s">
         <v>153</v>
       </c>
       <c r="V4" s="48"/>
       <c r="W4" s="48"/>
-      <c r="X4" s="963" t="s">
+      <c r="X4" s="966" t="s">
         <v>175</v>
       </c>
-      <c r="Y4" s="963" t="s">
+      <c r="Y4" s="966" t="s">
         <v>176</v>
       </c>
-      <c r="Z4" s="970" t="s">
+      <c r="Z4" s="964" t="s">
         <v>247</v>
       </c>
-      <c r="AA4" s="972" t="s">
+      <c r="AA4" s="968" t="s">
         <v>243</v>
       </c>
-      <c r="AB4" s="968" t="s">
+      <c r="AB4" s="962" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="300" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="966"/>
-      <c r="C5" s="964"/>
-      <c r="D5" s="962"/>
+      <c r="B5" s="975"/>
+      <c r="C5" s="973"/>
+      <c r="D5" s="972"/>
       <c r="E5" s="967"/>
-      <c r="F5" s="962"/>
-      <c r="G5" s="962"/>
-      <c r="H5" s="962"/>
+      <c r="F5" s="972"/>
+      <c r="G5" s="972"/>
+      <c r="H5" s="972"/>
       <c r="I5" s="967"/>
       <c r="J5" s="967"/>
       <c r="K5" s="967"/>
@@ -48572,12 +48553,12 @@
       <c r="Q5" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="962"/>
-      <c r="S5" s="962"/>
+      <c r="R5" s="972"/>
+      <c r="S5" s="972"/>
       <c r="T5" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="974"/>
+      <c r="U5" s="970"/>
       <c r="V5" s="80" t="s">
         <v>156</v>
       </c>
@@ -48586,9 +48567,9 @@
       </c>
       <c r="X5" s="967"/>
       <c r="Y5" s="967"/>
-      <c r="Z5" s="971"/>
-      <c r="AA5" s="973"/>
-      <c r="AB5" s="969"/>
+      <c r="Z5" s="965"/>
+      <c r="AA5" s="969"/>
+      <c r="AB5" s="963"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="21" t="s">
@@ -51871,10 +51852,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="330" t="str">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="331" t="str">
+      <c r="AA36" s="330">
+        <v>316.73400000000004</v>
+      </c>
+      <c r="AB36" s="331">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -52067,18 +52048,18 @@
       </c>
       <c r="AA38" s="332">
         <f>SUM(AA7:AA37)</f>
-        <v>6980.5560000000014</v>
+        <v>7297.2900000000018</v>
       </c>
       <c r="AB38" s="331">
         <f>IF(AA38=0,"0",(Z38*10/AA38))</f>
-        <v>12.318502996036417</v>
+        <v>11.783826598641411</v>
       </c>
       <c r="AC38" s="321">
         <v>10.199999999999999</v>
       </c>
       <c r="AD38" s="340">
         <f>AB38/AC38*100</f>
-        <v>120.76963721604331</v>
+        <v>115.52771175138639</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -52672,6 +52653,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="L4:L5"/>
@@ -52683,16 +52674,6 @@
     <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="AB6:AB38">
@@ -52730,15 +52711,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="975" t="s">
+      <c r="A1" s="976" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="976"/>
-      <c r="C1" s="976"/>
-      <c r="D1" s="977"/>
-      <c r="E1" s="976"/>
-      <c r="F1" s="976"/>
-      <c r="G1" s="978"/>
+      <c r="B1" s="977"/>
+      <c r="C1" s="977"/>
+      <c r="D1" s="978"/>
+      <c r="E1" s="977"/>
+      <c r="F1" s="977"/>
+      <c r="G1" s="979"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="9"/>
@@ -52751,7 +52732,7 @@
       <c r="D3" s="359"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="989" t="s">
+      <c r="A4" s="990" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -52763,19 +52744,19 @@
       <c r="D4" s="361" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="979" t="s">
+      <c r="E4" s="980" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="982" t="s">
+      <c r="F4" s="983" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="985" t="s">
+      <c r="G4" s="986" t="s">
         <v>253</v>
       </c>
-      <c r="H4" s="988"/>
+      <c r="H4" s="989"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="990"/>
+      <c r="A5" s="991"/>
       <c r="B5" s="34" t="s">
         <v>48</v>
       </c>
@@ -52785,20 +52766,20 @@
       <c r="D5" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="980"/>
-      <c r="F5" s="983"/>
-      <c r="G5" s="986"/>
-      <c r="H5" s="988"/>
+      <c r="E5" s="981"/>
+      <c r="F5" s="984"/>
+      <c r="G5" s="987"/>
+      <c r="H5" s="989"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="991"/>
+      <c r="A6" s="992"/>
       <c r="B6" s="40"/>
       <c r="C6" s="362"/>
       <c r="D6" s="361"/>
-      <c r="E6" s="981"/>
-      <c r="F6" s="984"/>
-      <c r="G6" s="987"/>
-      <c r="H6" s="988"/>
+      <c r="E6" s="982"/>
+      <c r="F6" s="985"/>
+      <c r="G6" s="988"/>
+      <c r="H6" s="989"/>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="687">
@@ -53691,11 +53672,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F36" s="747" t="str">
+      <c r="F36" s="747">
         <f>'PROD.FIG. '!H34</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="336" t="str">
+        <v>316.73400000000004</v>
+      </c>
+      <c r="G36" s="336">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -53751,18 +53732,18 @@
       </c>
       <c r="F38" s="358">
         <f>SUM(F7:F37)</f>
-        <v>6980.5560000000014</v>
+        <v>7297.2900000000018</v>
       </c>
       <c r="G38" s="338">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>31.560165121517535</v>
+        <v>30.190317227354257</v>
       </c>
       <c r="H38" s="335">
         <v>22</v>
       </c>
       <c r="I38" s="340">
         <f>G38/H38*100</f>
-        <v>143.45529600689787</v>
+        <v>137.22871466979208</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -53839,16 +53820,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="992" t="s">
+      <c r="A1" s="993" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="954"/>
-      <c r="C1" s="954"/>
-      <c r="D1" s="954"/>
-      <c r="E1" s="954"/>
-      <c r="F1" s="954"/>
-      <c r="G1" s="954"/>
-      <c r="H1" s="954"/>
+      <c r="B1" s="955"/>
+      <c r="C1" s="955"/>
+      <c r="D1" s="955"/>
+      <c r="E1" s="955"/>
+      <c r="F1" s="955"/>
+      <c r="G1" s="955"/>
+      <c r="H1" s="955"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="12"/>
@@ -54427,8 +54408,8 @@
       <c r="E34" s="687"/>
       <c r="F34" s="687"/>
       <c r="G34" s="687"/>
-      <c r="H34" s="690" t="str">
-        <v>0</v>
+      <c r="H34" s="690">
+        <v>316.73400000000004</v>
       </c>
       <c r="I34" s="298"/>
       <c r="J34" s="299"/>
@@ -54461,7 +54442,7 @@
       </c>
       <c r="H36" s="737">
         <f>SUM(H5:H35)</f>
-        <v>6980.5560000000014</v>
+        <v>7297.2900000000018</v>
       </c>
       <c r="I36" s="298"/>
       <c r="J36" s="299"/>
@@ -54577,11 +54558,11 @@
       <c r="D3" s="85"/>
       <c r="E3" s="85"/>
       <c r="F3" s="1"/>
-      <c r="I3" s="997" t="s">
+      <c r="I3" s="1006" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="998"/>
-      <c r="K3" s="999"/>
+      <c r="J3" s="1007"/>
+      <c r="K3" s="1008"/>
     </row>
     <row r="4" spans="1:24" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
@@ -54594,46 +54575,46 @@
         <v>250</v>
       </c>
       <c r="H4" s="347"/>
-      <c r="I4" s="1000" t="s">
+      <c r="I4" s="1009" t="s">
         <v>262</v>
       </c>
-      <c r="J4" s="1001"/>
-      <c r="K4" s="1002"/>
+      <c r="J4" s="1010"/>
+      <c r="K4" s="1011"/>
       <c r="M4" s="417"/>
       <c r="N4" s="417"/>
       <c r="O4" s="418"/>
       <c r="P4" s="418"/>
-      <c r="Q4" s="1012" t="s">
+      <c r="Q4" s="1021" t="s">
         <v>283</v>
       </c>
-      <c r="R4" s="1012"/>
-      <c r="S4" s="1012"/>
-      <c r="T4" s="1012"/>
+      <c r="R4" s="1021"/>
+      <c r="S4" s="1021"/>
+      <c r="T4" s="1021"/>
       <c r="U4" s="191"/>
       <c r="V4" s="417"/>
       <c r="W4" s="191"/>
       <c r="X4" s="191"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="941" t="s">
+      <c r="A5" s="942" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="943" t="s">
+      <c r="B5" s="944" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="943" t="s">
+      <c r="C5" s="944" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="1019" t="s">
+      <c r="D5" s="1000" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="1019" t="s">
+      <c r="E5" s="1000" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="1017" t="s">
+      <c r="F5" s="998" t="s">
         <v>243</v>
       </c>
-      <c r="G5" s="1014" t="s">
+      <c r="G5" s="995" t="s">
         <v>249</v>
       </c>
       <c r="I5" s="419" t="s">
@@ -54645,43 +54626,43 @@
       <c r="K5" s="421" t="s">
         <v>265</v>
       </c>
-      <c r="M5" s="1003" t="s">
+      <c r="M5" s="1012" t="s">
         <v>266</v>
       </c>
-      <c r="N5" s="1004"/>
-      <c r="O5" s="1005"/>
+      <c r="N5" s="1013"/>
+      <c r="O5" s="1014"/>
       <c r="P5" s="422"/>
-      <c r="Q5" s="1006" t="s">
+      <c r="Q5" s="1015" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="1008" t="s">
+      <c r="R5" s="1017" t="s">
         <v>267</v>
       </c>
-      <c r="S5" s="1009"/>
+      <c r="S5" s="1018"/>
       <c r="T5" s="453" t="s">
         <v>268</v>
       </c>
       <c r="U5" s="423" t="s">
         <v>269</v>
       </c>
-      <c r="V5" s="1010" t="s">
+      <c r="V5" s="1019" t="s">
         <v>277</v>
       </c>
-      <c r="W5" s="993" t="s">
+      <c r="W5" s="1002" t="s">
         <v>270</v>
       </c>
-      <c r="X5" s="995" t="s">
+      <c r="X5" s="1004" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1013"/>
-      <c r="B6" s="1016"/>
-      <c r="C6" s="1016"/>
-      <c r="D6" s="1020"/>
-      <c r="E6" s="1020"/>
-      <c r="F6" s="1018"/>
-      <c r="G6" s="1015"/>
+      <c r="A6" s="994"/>
+      <c r="B6" s="997"/>
+      <c r="C6" s="997"/>
+      <c r="D6" s="1001"/>
+      <c r="E6" s="1001"/>
+      <c r="F6" s="999"/>
+      <c r="G6" s="996"/>
       <c r="I6" s="424">
         <v>10</v>
       </c>
@@ -54700,7 +54681,7 @@
         <v>273</v>
       </c>
       <c r="P6" s="418"/>
-      <c r="Q6" s="1007"/>
+      <c r="Q6" s="1016"/>
       <c r="R6" s="448" t="s">
         <v>274</v>
       </c>
@@ -54713,9 +54694,9 @@
       <c r="U6" s="429" t="s">
         <v>275</v>
       </c>
-      <c r="V6" s="1011"/>
-      <c r="W6" s="994"/>
-      <c r="X6" s="996"/>
+      <c r="V6" s="1020"/>
+      <c r="W6" s="1003"/>
+      <c r="X6" s="1005"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="716">
@@ -56861,14 +56842,14 @@
         <v>0</v>
       </c>
       <c r="E36" s="717">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F36" s="718">
-        <v>0</v>
-      </c>
-      <c r="G36" s="336" t="str">
+        <v>316.73400000000004</v>
+      </c>
+      <c r="G36" s="336">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.0515574583088645</v>
       </c>
       <c r="I36" s="430">
         <v>310</v>
@@ -57011,15 +56992,15 @@
       </c>
       <c r="E38" s="714">
         <f>SUM(E7:E37)</f>
-        <v>36900</v>
+        <v>38500</v>
       </c>
       <c r="F38" s="715">
         <f>SUM(F7:F37)</f>
-        <v>6980.5560000000014</v>
+        <v>7297.2900000000018</v>
       </c>
       <c r="G38" s="345">
         <f>IF(F38=0,"0",(E38/F38))</f>
-        <v>5.2861118799132898</v>
+        <v>5.2759312018571265</v>
       </c>
       <c r="H38" s="348">
         <v>5</v>
@@ -57181,13 +57162,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="W5:W6"/>
     <mergeCell ref="X5:X6"/>
     <mergeCell ref="I3:K3"/>
@@ -57197,6 +57171,13 @@
     <mergeCell ref="R5:S5"/>
     <mergeCell ref="V5:V6"/>
     <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="G7:G38">
